--- a/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="62">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -123,7 +123,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>Level</t>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>Permis de conduire</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Tiers de confiance</t>
   </si>
 </sst>
 </file>
@@ -510,7 +516,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -635,6 +641,18 @@
       </c>
       <c r="D10" s="2"/>
     </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
+++ b/ig/nr-add-vs-cs-to-id/CodeSystem-fr-core-cs-mode-validation-identity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
